--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288044</v>
       </c>
       <c r="B4" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288044</v>
       </c>
       <c r="B4" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288044</v>
       </c>
       <c r="B4" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131288076</v>
       </c>
       <c r="B2" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131288038</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>131288044</v>
       </c>
       <c r="B4" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131288076</v>
+        <v>131288044</v>
       </c>
       <c r="B2" t="n">
-        <v>57092</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512514</v>
+        <v>512519</v>
       </c>
       <c r="R2" t="n">
-        <v>6697021</v>
+        <v>6697017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +751,13 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre tall, betad i kronan.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,33 +776,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131288038</v>
+        <v>131288076</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512530</v>
+        <v>512514</v>
       </c>
       <c r="R3" t="n">
-        <v>6697034</v>
+        <v>6697021</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,13 +857,17 @@
           <t>2026-02-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre tall, betad i kronan.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,107 +883,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>131288044</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91801</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Smedsberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>512519</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6697017</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4682-2025 artfynd.xlsx
+++ b/artfynd/A 4682-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,8 +893,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131288076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>